--- a/РАБОЧИЙ СТОЛ/расчеты Останкино КИ/дв 10,08,26 млрсч ост ки.xlsx
+++ b/РАБОЧИЙ СТОЛ/расчеты Останкино КИ/дв 10,08,26 млрсч ост ки.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчеты Останкино КИ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\РАБОЧИЙ СТОЛ\расчеты Останкино КИ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16597C0A-D85E-42AF-A0A0-A68AF46B1778}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C11B052-6E9C-4397-A5F8-56763BAE8643}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,15 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet!$A$3:$AE$113</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
@@ -1790,7 +1782,7 @@
         <v>38.653199999999998</v>
       </c>
       <c r="Q9" s="5">
-        <f t="shared" ref="Q7:Q17" si="7">15*P9-O9-F9</f>
+        <f t="shared" ref="Q9:Q17" si="7">15*P9-O9-F9</f>
         <v>120.75099999999998</v>
       </c>
       <c r="R9" s="1">
@@ -2992,7 +2984,7 @@
         <v>25</v>
       </c>
       <c r="Q20" s="5">
-        <f t="shared" ref="Q19:Q23" si="8">15*P20-O20-F20</f>
+        <f t="shared" ref="Q20:Q21" si="8">15*P20-O20-F20</f>
         <v>207</v>
       </c>
       <c r="R20" s="1">
@@ -3642,7 +3634,7 @@
         <v>9.1999999999999993</v>
       </c>
       <c r="Q26" s="5">
-        <f t="shared" ref="Q25:Q31" si="10">15*P26-O26-F26</f>
+        <f t="shared" ref="Q26" si="10">15*P26-O26-F26</f>
         <v>68</v>
       </c>
       <c r="R26" s="1">
@@ -5038,7 +5030,7 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="Q39" s="5">
-        <f t="shared" ref="Q39:Q44" si="16">15*P39-O39-F39</f>
+        <f t="shared" ref="Q39:Q43" si="16">15*P39-O39-F39</f>
         <v>22</v>
       </c>
       <c r="R39" s="1">
@@ -6872,7 +6864,7 @@
         <v>12.2</v>
       </c>
       <c r="Q56" s="5">
-        <f t="shared" ref="Q56:Q57" si="20">15*P56-O56-F56</f>
+        <f t="shared" ref="Q56" si="20">15*P56-O56-F56</f>
         <v>53</v>
       </c>
       <c r="R56" s="1">
@@ -7500,7 +7492,7 @@
         <v>13.817599999999999</v>
       </c>
       <c r="Q62" s="5">
-        <f t="shared" ref="Q61:Q71" si="22">15*P62-O62-F62</f>
+        <f t="shared" ref="Q62:Q70" si="22">15*P62-O62-F62</f>
         <v>3.8899999999999793</v>
       </c>
       <c r="R62" s="1">
@@ -10623,7 +10615,7 @@
         <v>21.6</v>
       </c>
       <c r="Q91" s="5">
-        <f t="shared" ref="Q90:Q91" si="29">15*P91-O91-F91</f>
+        <f t="shared" ref="Q91" si="29">15*P91-O91-F91</f>
         <v>143</v>
       </c>
       <c r="R91" s="1">
@@ -11142,7 +11134,7 @@
         <v>8.8000000000000007</v>
       </c>
       <c r="Q96" s="5">
-        <f t="shared" ref="Q95:Q98" si="30">15*P96-O96-F96</f>
+        <f t="shared" ref="Q96" si="30">15*P96-O96-F96</f>
         <v>38</v>
       </c>
       <c r="R96" s="1">
@@ -11649,7 +11641,7 @@
         <v>5.2</v>
       </c>
       <c r="Q101" s="5">
-        <f t="shared" ref="Q101:Q102" si="31">15*P101-O101-F101</f>
+        <f t="shared" ref="Q101" si="31">15*P101-O101-F101</f>
         <v>39</v>
       </c>
       <c r="R101" s="1">
@@ -11746,7 +11738,7 @@
         <v>29</v>
       </c>
       <c r="L102" s="1">
-        <f t="shared" ref="L102:L133" si="32">E102-K102</f>
+        <f t="shared" ref="L102:L113" si="32">E102-K102</f>
         <v>-3</v>
       </c>
       <c r="M102" s="1"/>
@@ -11760,7 +11752,7 @@
       </c>
       <c r="Q102" s="5"/>
       <c r="R102" s="1">
-        <f t="shared" ref="R102:R133" si="34">(F102+O102+Q102)/P102</f>
+        <f t="shared" ref="R102:R113" si="34">(F102+O102+Q102)/P102</f>
         <v>28.46153846153846</v>
       </c>
       <c r="S102" s="1">
@@ -12065,7 +12057,7 @@
         <v>18.600000000000001</v>
       </c>
       <c r="Q105" s="5">
-        <f t="shared" ref="Q104:Q112" si="37">15*P105-O105-F105</f>
+        <f t="shared" ref="Q105:Q111" si="37">15*P105-O105-F105</f>
         <v>108</v>
       </c>
       <c r="R105" s="1">
